--- a/AAII_Financials/Yearly/LE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/LE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>LE</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45324</v>
+      </c>
+      <c r="E7" s="2">
         <v>44953</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44589</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44225</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43861</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43497</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43133</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42762</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42398</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42034</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41670</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41306</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40935</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1472500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1555400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1636600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1427400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1450200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1451600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1406700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1335800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1419800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1555400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1562900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1585900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1725600</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>847000</v>
+      </c>
+      <c r="E9" s="3">
         <v>961700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>945200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>821600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>828300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>835500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>809500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>759400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>767200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>819400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>852500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>881800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>959600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>625500</v>
+      </c>
+      <c r="E10" s="3">
         <v>593800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>691500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>605900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>621900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>616100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>597200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>576400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>652600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>735900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>710300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>704100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>766000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,8 +878,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,9 +920,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,39 +965,42 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>113400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>6800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>173000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>98300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
@@ -990,51 +1010,57 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E15" s="3">
         <v>38700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>39200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>37300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>31100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22700</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1048,92 +1074,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1556700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1530700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1556800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1386300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1404800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1409000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1377600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1488400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1424900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1415700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1434500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1503900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1603800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-84200</v>
+      </c>
+      <c r="E18" s="3">
         <v>24700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>79800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>42600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>29100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-152600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>139600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>128300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>82000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>121800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,40 +1183,41 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
@@ -1191,177 +1225,192 @@
       <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E21" s="3">
         <v>63800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>119600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>77700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>78500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>66100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>51300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-135200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>160800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>150000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>105200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>144600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E22" s="3">
         <v>39800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-131800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>46000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-178900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>120600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>128400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>82100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-69100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-9700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>46800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>49500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1401,93 +1450,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-109800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>78800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>76200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>33400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-109800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>78800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>49800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>76200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1527,9 +1585,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,15 +1606,15 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>3700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>29700</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1569,9 +1630,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1611,9 +1675,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1653,41 +1720,44 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
@@ -1695,51 +1765,57 @@
       <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>33400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-109800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>78800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>49800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>76200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1779,98 +1855,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>33400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-109800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>78800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>49800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>76200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45324</v>
+      </c>
+      <c r="E38" s="2">
         <v>44953</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44589</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44225</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43861</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43497</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43133</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42762</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42398</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42034</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41670</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41306</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40935</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1887,8 +1972,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1905,50 +1991,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E41" s="3">
         <v>39600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>195600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>213100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>228400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>221500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1988,177 +2078,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E43" s="3">
         <v>44900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>49700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>37600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>32100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>301700</v>
+      </c>
+      <c r="E44" s="3">
         <v>425500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>384200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>382100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>375700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>321900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>332300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>325300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>329200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>301400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>369900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>378500</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E45" s="3">
         <v>46700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>42200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>29000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>410300</v>
+      </c>
+      <c r="E46" s="3">
         <v>556700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>506900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>495800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>545400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>588400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>606800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>607400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>616500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>587600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>451200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>463200</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2198,56 +2303,62 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E48" s="3">
         <v>158000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>161300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>180800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>196300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>149900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>136500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>122800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>219700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>101200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>109700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>363700</v>
+        <v>257000</v>
       </c>
       <c r="E49" s="3">
         <v>363700</v>
@@ -2256,7 +2367,7 @@
         <v>363700</v>
       </c>
       <c r="G49" s="3">
-        <v>367000</v>
+        <v>363700</v>
       </c>
       <c r="H49" s="3">
         <v>367000</v>
@@ -2268,23 +2379,26 @@
         <v>367000</v>
       </c>
       <c r="K49" s="3">
+        <v>367000</v>
+      </c>
+      <c r="L49" s="3">
         <v>540000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>638700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1172700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>644000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2324,9 +2438,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2366,51 +2483,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E52" s="3">
         <v>3800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2450,51 +2573,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>811500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1082100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1036600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1045500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1113600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1110900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1124100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1114400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1281500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1350000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1194300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1217700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2511,8 +2640,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2529,55 +2659,59 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E57" s="3">
         <v>171600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>145800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>134000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>158400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>123800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>155900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>162400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>146100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>132800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>115400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>106700</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13800</v>
+        <v>13000</v>
       </c>
       <c r="E58" s="3">
         <v>13800</v>
@@ -2586,7 +2720,7 @@
         <v>13800</v>
       </c>
       <c r="G58" s="3">
-        <v>5200</v>
+        <v>13800</v>
       </c>
       <c r="H58" s="3">
         <v>5200</v>
@@ -2603,8 +2737,8 @@
       <c r="L58" s="3">
         <v>5200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>5200</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -2612,177 +2746,192 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E59" s="3">
         <v>112200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>151900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>167200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>120000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>112300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>95100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>162800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>102400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>88000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>87100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>259900</v>
+      </c>
+      <c r="E60" s="3">
         <v>297500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>311400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>314900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>283600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>241300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>256100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>248900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>230100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>240300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>203400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>193700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>236200</v>
+      </c>
+      <c r="E61" s="3">
         <v>323500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>234500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>270600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>378700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>482500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>486200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>490000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>493800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>506000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E62" s="3">
         <v>80400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>84000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>90300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>103000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>64500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>74700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>104100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>173100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>199500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>198600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2822,9 +2971,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2864,9 +3016,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2906,51 +3061,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>569900</v>
+      </c>
+      <c r="E66" s="3">
         <v>701400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>629900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>675800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>765200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>788200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>817000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>843000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>897000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>945800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>402000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>394500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2967,8 +3128,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3008,9 +3170,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3050,9 +3215,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3092,9 +3260,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3134,51 +3305,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-99400</v>
+      </c>
+      <c r="E72" s="3">
         <v>31300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-29800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-60500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>68900</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3218,9 +3395,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3260,9 +3440,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3302,51 +3485,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E76" s="3">
         <v>380800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>406700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>369700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>348400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>322700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>307100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>271400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>384500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>404200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>792300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>823200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3386,98 +3575,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45324</v>
+      </c>
+      <c r="E80" s="2">
         <v>44953</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44589</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44225</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43861</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43497</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43133</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42762</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42398</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42034</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41670</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41306</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40935</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>33400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-109800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>78800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>49800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>76200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3494,50 +3692,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E83" s="3">
         <v>38700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>37300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>22700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3577,9 +3779,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3619,9 +3824,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3661,9 +3869,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3703,9 +3914,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3745,51 +3959,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-36400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>91600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>48200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>211100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>114900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>96200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3806,50 +4026,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15100</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3889,9 +4113,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3931,51 +4158,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-38000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3992,8 +4225,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4033,9 +4267,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4075,9 +4312,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4117,9 +4357,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4159,133 +4402,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-110100</v>
+      </c>
+      <c r="E100" s="3">
         <v>73500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-45100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-103100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-105900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-5200</v>
       </c>
       <c r="K100" s="3">
         <v>-5200</v>
       </c>
       <c r="L100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M100" s="3">
         <v>8200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-110900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-68800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3700</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-116100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>199000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>LE</t>
   </si>
@@ -975,25 +975,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>113400</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>120900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3500</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>6800</v>
+        <v>7900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>173000</v>
@@ -1081,16 +1081,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1556700</v>
+        <v>1435800</v>
       </c>
       <c r="E17" s="3">
-        <v>1530700</v>
+        <v>1527200</v>
       </c>
       <c r="F17" s="3">
         <v>1556800</v>
       </c>
       <c r="G17" s="3">
-        <v>1386300</v>
+        <v>1378400</v>
       </c>
       <c r="H17" s="3">
         <v>1404800</v>
@@ -1126,16 +1126,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-84200</v>
+        <v>36800</v>
       </c>
       <c r="E18" s="3">
-        <v>24700</v>
+        <v>28200</v>
       </c>
       <c r="F18" s="3">
         <v>79800</v>
       </c>
       <c r="G18" s="3">
-        <v>41100</v>
+        <v>49000</v>
       </c>
       <c r="H18" s="3">
         <v>45400</v>
@@ -1190,25 +1190,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>700</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>600</v>
+        <v>-600</v>
       </c>
       <c r="G20" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>-1900</v>
       </c>
       <c r="I20" s="3">
-        <v>-4100</v>
+        <v>4100</v>
       </c>
       <c r="J20" s="3">
-        <v>-2700</v>
+        <v>2700</v>
       </c>
       <c r="K20" s="3">
         <v>-1600</v>
@@ -1235,16 +1235,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-45100</v>
+        <v>75900</v>
       </c>
       <c r="E21" s="3">
-        <v>63800</v>
+        <v>67300</v>
       </c>
       <c r="F21" s="3">
         <v>119600</v>
       </c>
       <c r="G21" s="3">
-        <v>77700</v>
+        <v>85600</v>
       </c>
       <c r="H21" s="3">
         <v>78500</v>
@@ -1385,10 +1385,10 @@
         <v>2100</v>
       </c>
       <c r="I24" s="3">
-        <v>1700</v>
+        <v>-2000</v>
       </c>
       <c r="J24" s="3">
-        <v>2000</v>
+        <v>-27700</v>
       </c>
       <c r="K24" s="3">
         <v>-69100</v>
@@ -1475,10 +1475,10 @@
         <v>19300</v>
       </c>
       <c r="I26" s="3">
-        <v>7900</v>
+        <v>11600</v>
       </c>
       <c r="J26" s="3">
-        <v>-1500</v>
+        <v>28200</v>
       </c>
       <c r="K26" s="3">
         <v>-109800</v>
@@ -1520,10 +1520,10 @@
         <v>19300</v>
       </c>
       <c r="I27" s="3">
-        <v>7900</v>
+        <v>11600</v>
       </c>
       <c r="J27" s="3">
-        <v>-1500</v>
+        <v>28200</v>
       </c>
       <c r="K27" s="3">
         <v>-109800</v>
@@ -1594,26 +1594,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1730,25 +1730,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-700</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="G32" s="3">
-        <v>800</v>
+        <v>-800</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>1900</v>
       </c>
       <c r="I32" s="3">
-        <v>4100</v>
+        <v>-4100</v>
       </c>
       <c r="J32" s="3">
-        <v>2700</v>
+        <v>-2700</v>
       </c>
       <c r="K32" s="3">
         <v>1600</v>
@@ -2178,25 +2178,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>47900</v>
+        <v>10300</v>
       </c>
       <c r="E45" s="3">
-        <v>46700</v>
+        <v>10400</v>
       </c>
       <c r="F45" s="3">
-        <v>38700</v>
+        <v>10800</v>
       </c>
       <c r="G45" s="3">
-        <v>42200</v>
+        <v>10200</v>
       </c>
       <c r="H45" s="3">
-        <v>41600</v>
+        <v>14700</v>
       </c>
       <c r="I45" s="3">
-        <v>38500</v>
+        <v>13500</v>
       </c>
       <c r="J45" s="3">
-        <v>29000</v>
+        <v>13700</v>
       </c>
       <c r="K45" s="3">
         <v>29700</v>
@@ -2267,26 +2267,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2711,19 +2711,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="E58" s="3">
-        <v>13800</v>
+        <v>19200</v>
       </c>
       <c r="F58" s="3">
-        <v>13800</v>
+        <v>19400</v>
       </c>
       <c r="G58" s="3">
-        <v>13800</v>
+        <v>18900</v>
       </c>
       <c r="H58" s="3">
-        <v>5200</v>
+        <v>11000</v>
       </c>
       <c r="I58" s="3">
         <v>5200</v>
@@ -2756,25 +2756,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>115000</v>
+        <v>69700</v>
       </c>
       <c r="E59" s="3">
-        <v>112200</v>
+        <v>74400</v>
       </c>
       <c r="F59" s="3">
-        <v>151900</v>
+        <v>73100</v>
       </c>
       <c r="G59" s="3">
-        <v>167200</v>
+        <v>82100</v>
       </c>
       <c r="H59" s="3">
-        <v>120000</v>
+        <v>62100</v>
       </c>
       <c r="I59" s="3">
-        <v>112300</v>
+        <v>60700</v>
       </c>
       <c r="J59" s="3">
-        <v>95100</v>
+        <v>56100</v>
       </c>
       <c r="K59" s="3">
         <v>81300</v>
@@ -2846,19 +2846,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>236200</v>
+        <v>259100</v>
       </c>
       <c r="E61" s="3">
-        <v>323500</v>
+        <v>354600</v>
       </c>
       <c r="F61" s="3">
-        <v>234500</v>
+        <v>267200</v>
       </c>
       <c r="G61" s="3">
-        <v>270600</v>
+        <v>308400</v>
       </c>
       <c r="H61" s="3">
-        <v>378700</v>
+        <v>418500</v>
       </c>
       <c r="I61" s="3">
         <v>482500</v>
@@ -2891,25 +2891,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>73800</v>
+        <v>2800</v>
       </c>
       <c r="E62" s="3">
-        <v>80400</v>
+        <v>3400</v>
       </c>
       <c r="F62" s="3">
-        <v>84000</v>
+        <v>5100</v>
       </c>
       <c r="G62" s="3">
-        <v>90300</v>
+        <v>5100</v>
       </c>
       <c r="H62" s="3">
-        <v>103000</v>
+        <v>5500</v>
       </c>
       <c r="I62" s="3">
-        <v>64500</v>
+        <v>5800</v>
       </c>
       <c r="J62" s="3">
-        <v>74700</v>
+        <v>15500</v>
       </c>
       <c r="K62" s="3">
         <v>104100</v>

--- a/AAII_Financials/Yearly/LE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>LE</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45324</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44953</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44589</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44225</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43861</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43497</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43133</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42762</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42398</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42034</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41670</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41306</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40935</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1362900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1472500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1555400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1636600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1427400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1450200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1451600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1406700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1335800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1419800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1555400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1562900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1585900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1725600</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>709600</v>
+      </c>
+      <c r="E9" s="3">
         <v>847000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>961700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>945200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>821600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>828300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>835500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>809500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>759400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>767200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>819400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>852500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>881800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>959600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>653300</v>
+      </c>
+      <c r="E10" s="3">
         <v>625500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>593800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>691500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>605900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>621900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>616100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>597200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>576400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>652600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>735900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>710300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>704100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>766000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -879,8 +892,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -923,9 +937,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -968,42 +985,45 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>120900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>7900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>173000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>98300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1013,54 +1033,60 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E15" s="3">
         <v>38500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>39200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>37300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>31100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>27600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22700</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1075,98 +1101,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1312000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1435800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1527200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1556800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1378400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1404800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1409000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1377600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1488400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1424900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1415700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1434500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1503900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1603800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E18" s="3">
         <v>36800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>28200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>79800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>49000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>42600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-152600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>139600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>128300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>82000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>121800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1184,43 +1217,44 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1228,189 +1262,204 @@
       <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E21" s="3">
         <v>75900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>67300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>119600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>85600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>78500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>66100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>51300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-135200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>160800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>150000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>105200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>144600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E22" s="3">
         <v>48300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20500</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-131800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>46000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-178900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-29200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>120600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>128400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>82100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-27700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-69100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-9700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>49500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>45700</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1453,99 +1502,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-130700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>33400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-109800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>78800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>76200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-130700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>33400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-109800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>78800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>49800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>76200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1588,9 +1646,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1633,9 +1694,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1678,9 +1742,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1723,44 +1790,47 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -1768,54 +1838,60 @@
       <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-130700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>33400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-109800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>73800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>78800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>49800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>76200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1858,104 +1934,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-130700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>33400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-109800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>73800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>78800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>49800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>76200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45324</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44953</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44589</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44225</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43861</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43497</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43133</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42762</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42398</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42034</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41670</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41306</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40935</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1973,8 +2058,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1992,53 +2078,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E41" s="3">
         <v>25300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>193400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>195600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>213100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>228400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>221500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2081,189 +2171,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E43" s="3">
         <v>35300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>44900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>49700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>37600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>32100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>265100</v>
+      </c>
+      <c r="E44" s="3">
         <v>301700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>425500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>384200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>382100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>375700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>321900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>332300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>325300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>329200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>301400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>369900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>378500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E45" s="3">
         <v>10300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>370500</v>
+      </c>
+      <c r="E46" s="3">
         <v>410300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>556700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>506900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>495800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>545400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>588400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>606800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>607400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>616500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>587600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>451200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>463200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2288,8 +2393,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2306,54 +2411,60 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E48" s="3">
         <v>141500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>158000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>161300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>180800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>196300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>149900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>136500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>122800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>219700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>109700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2361,7 +2472,7 @@
         <v>257000</v>
       </c>
       <c r="E49" s="3">
-        <v>363700</v>
+        <v>257000</v>
       </c>
       <c r="F49" s="3">
         <v>363700</v>
@@ -2370,7 +2481,7 @@
         <v>363700</v>
       </c>
       <c r="H49" s="3">
-        <v>367000</v>
+        <v>363700</v>
       </c>
       <c r="I49" s="3">
         <v>367000</v>
@@ -2382,23 +2493,26 @@
         <v>367000</v>
       </c>
       <c r="L49" s="3">
+        <v>367000</v>
+      </c>
+      <c r="M49" s="3">
         <v>540000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>638700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1172700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>644000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2441,9 +2555,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2486,54 +2603,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2576,54 +2699,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>765500</v>
+      </c>
+      <c r="E54" s="3">
         <v>811500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1082100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1036600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1045500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1113600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1110900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1124100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1114400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1281500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1350000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1194300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1217700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2641,8 +2770,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2660,73 +2790,77 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E57" s="3">
         <v>131900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>171600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>145800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>134000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>158400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>123800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>155900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>162400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>146100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>132800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>115400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>106700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E58" s="3">
         <v>19000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5200</v>
       </c>
       <c r="J58" s="3">
         <v>5200</v>
@@ -2740,8 +2874,8 @@
       <c r="M58" s="3">
         <v>5200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
+      <c r="N58" s="3">
+        <v>5200</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -2749,189 +2883,204 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>69700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>74400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>62100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>60700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>162800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>88000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>87100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E60" s="3">
         <v>259900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>297500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>311400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>314900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>283600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>241300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>256100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>248900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>230100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>240300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>203400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>193700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>244900</v>
+      </c>
+      <c r="E61" s="3">
         <v>259100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>354600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>267200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>308400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>418500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>482500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>486200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>490000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>493800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>506000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5100</v>
       </c>
       <c r="G62" s="3">
         <v>5100</v>
       </c>
       <c r="H62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I62" s="3">
         <v>5500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>104100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>173100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>199500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>198600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2974,9 +3123,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3019,9 +3171,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3064,54 +3219,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>526300</v>
+      </c>
+      <c r="E66" s="3">
         <v>569900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>701400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>629900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>675800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>765200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>788200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>817000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>843000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>897000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>945800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>402000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>394500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3129,8 +3290,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3173,9 +3335,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3218,9 +3383,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3263,9 +3431,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3308,54 +3479,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-94400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-99400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>44600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-60500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>68900</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3398,9 +3575,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3443,9 +3623,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3488,54 +3671,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>239200</v>
+      </c>
+      <c r="E76" s="3">
         <v>241600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>380800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>369700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>348400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>322700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>307100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>384500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>404200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>792300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>823200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3578,104 +3767,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45324</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44953</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44589</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44225</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43861</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43497</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43133</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42762</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42398</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42034</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41670</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41306</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40935</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-130700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>33400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-109800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>73800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>78800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>49800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>76200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3693,53 +3891,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E83" s="3">
         <v>38500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>22700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3782,9 +3984,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3827,9 +4032,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3872,9 +4080,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3917,9 +4128,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3962,54 +4176,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E89" s="3">
         <v>130600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-36400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>70600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>91600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>48200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>211100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>114900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>96200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4027,53 +4247,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4116,9 +4340,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4161,54 +4388,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-38000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4226,8 +4459,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4270,9 +4504,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4315,9 +4552,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4360,9 +4600,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4405,142 +4648,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-110100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>73500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-45100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-103100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-105900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-5200</v>
       </c>
       <c r="L100" s="3">
         <v>-5200</v>
       </c>
       <c r="M100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="N100" s="3">
         <v>8200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-110900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-68800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3700</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-116100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>199000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>LE</t>
   </si>
@@ -994,14 +994,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>9400</v>
       </c>
       <c r="E14" s="3">
-        <v>120900</v>
+        <v>120500</v>
       </c>
       <c r="F14" s="3">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1108,13 +1108,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1312000</v>
+        <v>1302600</v>
       </c>
       <c r="E17" s="3">
-        <v>1435800</v>
+        <v>1436200</v>
       </c>
       <c r="F17" s="3">
-        <v>1527200</v>
+        <v>1527700</v>
       </c>
       <c r="G17" s="3">
         <v>1556800</v>
@@ -1156,13 +1156,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>51000</v>
+        <v>60300</v>
       </c>
       <c r="E18" s="3">
-        <v>36800</v>
+        <v>36300</v>
       </c>
       <c r="F18" s="3">
-        <v>28200</v>
+        <v>27700</v>
       </c>
       <c r="G18" s="3">
         <v>79800</v>
@@ -1272,13 +1272,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>84700</v>
+        <v>94100</v>
       </c>
       <c r="E21" s="3">
-        <v>75900</v>
+        <v>75400</v>
       </c>
       <c r="F21" s="3">
-        <v>67300</v>
+        <v>66800</v>
       </c>
       <c r="G21" s="3">
         <v>119600</v>
@@ -2277,10 +2277,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5400</v>
+        <v>15500</v>
       </c>
       <c r="E45" s="3">
-        <v>10300</v>
+        <v>18300</v>
       </c>
       <c r="F45" s="3">
         <v>10400</v>
@@ -2892,8 +2892,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>63600</v>
       </c>
       <c r="E59" s="3">
         <v>69700</v>

--- a/AAII_Financials/Yearly/LE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>LE</t>
   </si>
@@ -656,225 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45324</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44953</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44589</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44225</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43861</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43497</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43133</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42762</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42398</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42034</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41670</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41306</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40935</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1335100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1362900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1472500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1555400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1636600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1427400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1450200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1451600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1406700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1335800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1419800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1555400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1562900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1585900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1725600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E9" s="3">
         <v>709600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>847000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>961700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>945200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>821600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>828300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>835500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>809500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>759400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>767200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>819400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>852500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>881800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>959600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>650200</v>
+      </c>
+      <c r="E10" s="3">
         <v>653300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>625500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>593800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>691500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>605900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>621900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>616100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>597200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>576400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>652600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>735900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>710300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>704100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>766000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -893,8 +905,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -940,9 +953,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -988,45 +1004,48 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E14" s="3">
         <v>9400</v>
       </c>
-      <c r="E14" s="3">
-        <v>120500</v>
-      </c>
       <c r="F14" s="3">
+        <v>121000</v>
+      </c>
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>7900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>173000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>98300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1036,57 +1055,63 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E15" s="3">
         <v>33800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>38700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>39200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>31100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>22700</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1102,104 +1127,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1276600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1302600</v>
       </c>
-      <c r="E17" s="3">
-        <v>1436200</v>
-      </c>
       <c r="F17" s="3">
+        <v>1435700</v>
+      </c>
+      <c r="G17" s="3">
         <v>1527700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1556800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1378400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1404800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1409000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1377600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1488400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1424900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1415700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1434500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1503900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1603800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E18" s="3">
         <v>60300</v>
       </c>
-      <c r="E18" s="3">
-        <v>36300</v>
-      </c>
       <c r="F18" s="3">
+        <v>36800</v>
+      </c>
+      <c r="G18" s="3">
         <v>27700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>79800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>49000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>42600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>29100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-152600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>139600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>128300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>82000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>121800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1218,46 +1250,47 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
@@ -1265,201 +1298,216 @@
       <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E21" s="3">
         <v>94100</v>
       </c>
-      <c r="E21" s="3">
-        <v>75400</v>
-      </c>
       <c r="F21" s="3">
+        <v>75900</v>
+      </c>
+      <c r="G21" s="3">
         <v>66800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>119600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>85600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>78500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>51300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-135200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>160800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>150000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>105200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>144600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E22" s="3">
         <v>40400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>48300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E23" s="3">
         <v>10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-131800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>46000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-178900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-29200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>120600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>128400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>82100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>121900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>4300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-27700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-69100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-9700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>49500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>45700</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1505,105 +1553,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>6200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-130700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>33400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-109800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>73800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>78800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>76200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E27" s="3">
         <v>6200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-130700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>33400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-109800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>73800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>78800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>49800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>76200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1649,9 +1706,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1697,9 +1757,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1745,9 +1808,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1793,47 +1859,50 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
@@ -1841,57 +1910,63 @@
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E33" s="3">
         <v>6200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-130700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>33400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-109800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>73800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>78800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>49800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>76200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1937,110 +2012,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E35" s="3">
         <v>6200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-130700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>33400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-109800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>73800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>78800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>49800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>76200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45324</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44953</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44589</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44225</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43861</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43497</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43133</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42762</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42398</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42034</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41670</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41306</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40935</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2059,8 +2143,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2079,56 +2164,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E41" s="3">
         <v>16200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>77100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>195600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>213100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>228400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>221500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>28300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2174,201 +2263,216 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E43" s="3">
         <v>47800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>35300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>44900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>51000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>32100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>268800</v>
+      </c>
+      <c r="E44" s="3">
         <v>265100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>301700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>425500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>384200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>382100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>375700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>321900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>332300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>325300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>329200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>301400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>369900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>378500</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E45" s="3">
         <v>15500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E46" s="3">
         <v>370500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>410300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>556700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>506900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>495800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>545400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>588400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>606800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>607400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>616500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>587600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>451200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>463200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2396,8 +2500,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2414,68 +2518,74 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>131400</v>
+      </c>
+      <c r="E48" s="3">
         <v>136000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>141500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>158000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>161300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>196300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>149900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>136500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>122800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>219700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>101100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>109700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>257000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>257000</v>
       </c>
       <c r="F49" s="3">
-        <v>363700</v>
+        <v>257000</v>
       </c>
       <c r="G49" s="3">
         <v>363700</v>
@@ -2484,7 +2594,7 @@
         <v>363700</v>
       </c>
       <c r="I49" s="3">
-        <v>367000</v>
+        <v>363700</v>
       </c>
       <c r="J49" s="3">
         <v>367000</v>
@@ -2496,23 +2606,26 @@
         <v>367000</v>
       </c>
       <c r="M49" s="3">
+        <v>367000</v>
+      </c>
+      <c r="N49" s="3">
         <v>540000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>638700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1172700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>644000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2558,9 +2671,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2606,57 +2722,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>258700</v>
+      </c>
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2702,57 +2824,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>751100</v>
+      </c>
+      <c r="E54" s="3">
         <v>765500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>811500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1082100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1036600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1045500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1113600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1110900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1124100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1114400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1281500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1350000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1194300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1217700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2771,8 +2899,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2791,79 +2920,83 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E57" s="3">
         <v>111400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>131900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>171600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>145800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>134000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>158400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>123800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>155900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>162400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>146100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>132800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>115400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>106700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E58" s="3">
         <v>17500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>5200</v>
       </c>
       <c r="K58" s="3">
         <v>5200</v>
@@ -2877,8 +3010,8 @@
       <c r="N58" s="3">
         <v>5200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
+      <c r="O58" s="3">
+        <v>5200</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -2886,201 +3019,216 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E59" s="3">
         <v>63600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>69700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>74400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>82100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>62100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>81300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>162800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>102400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>88000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>87100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>223900</v>
+      </c>
+      <c r="E60" s="3">
         <v>227600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>259900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>297500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>311400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>314900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>283600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>241300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>256100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>248900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>230100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>240300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>203400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>193700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>228500</v>
+      </c>
+      <c r="E61" s="3">
         <v>244900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>259100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>354600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>267200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>308400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>418500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>482500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>486200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>490000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>493800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>506000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>5100</v>
       </c>
       <c r="H62" s="3">
         <v>5100</v>
       </c>
       <c r="I62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J62" s="3">
         <v>5500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>104100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>173100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>199500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>198600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>200800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3126,9 +3274,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3174,9 +3325,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3222,57 +3376,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>506800</v>
+      </c>
+      <c r="E66" s="3">
         <v>526300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>569900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>701400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>629900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>675800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>765200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>788200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>817000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>843000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>897000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>945800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>402000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>394500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3291,8 +3451,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3338,9 +3499,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3386,9 +3550,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3434,9 +3601,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3482,57 +3652,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-88900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-94400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-99400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>44600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-60500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>68900</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3578,9 +3754,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3626,9 +3805,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3674,57 +3856,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E76" s="3">
         <v>239200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>241600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>380800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>406700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>369700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>348400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>322700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>307100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>384500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>404200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>792300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>823200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3770,110 +3958,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45324</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44953</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44589</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44225</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43861</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43497</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43133</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42762</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42398</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42034</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41670</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41306</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40935</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E81" s="3">
         <v>6200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-130700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>33400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-109800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>73800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>78800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>49800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>76200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3892,56 +4089,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E83" s="3">
         <v>33800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>38700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>39200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>19700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3987,9 +4188,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4035,9 +4239,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4083,9 +4290,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4131,9 +4341,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4179,57 +4392,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E89" s="3">
         <v>53100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>130600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-36400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>70600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>91600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>48200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>211100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>114900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>96200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4248,56 +4467,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4343,9 +4566,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4391,57 +4617,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-38100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4460,8 +4692,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4507,9 +4740,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4555,9 +4791,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4603,9 +4842,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4651,151 +4893,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-110100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>73500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-45100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-103100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-105900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-5200</v>
       </c>
       <c r="M100" s="3">
         <v>-5200</v>
       </c>
       <c r="N100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="O100" s="3">
         <v>8200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-110900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-68800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3700</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-116100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>199000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
